--- a/iwpb-sg-dashboard/sample/IWPB_PBT_L2_Driller.xlsx
+++ b/iwpb-sg-dashboard/sample/IWPB_PBT_L2_Driller.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW38"/>
+  <dimension ref="A1:AW42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2961,22 +2961,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MP20101010000</t>
+          <t>MP10301010000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Staff Costs</t>
+          <t>Insurance Manufacturing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Direct Costs</t>
+          <t>Net Insurance Revenue</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Total Direct Cost</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3025,133 +3025,133 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>-24.4</v>
+        <v>9.1</v>
       </c>
       <c r="O15" t="n">
-        <v>-19.7</v>
+        <v>7.4</v>
       </c>
       <c r="P15" t="n">
-        <v>-28.9</v>
+        <v>10.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>-31.2</v>
+        <v>11.7</v>
       </c>
       <c r="R15" t="n">
-        <v>-16.5</v>
+        <v>6.2</v>
       </c>
       <c r="S15" t="n">
-        <v>-19.8</v>
+        <v>7.4</v>
       </c>
       <c r="T15" t="n">
-        <v>-24.2</v>
+        <v>9.1</v>
       </c>
       <c r="U15" t="n">
-        <v>-23.7</v>
+        <v>8.9</v>
       </c>
       <c r="V15" t="n">
-        <v>-21.1</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>-18.4</v>
+        <v>6.9</v>
       </c>
       <c r="X15" t="n">
-        <v>-32.6</v>
+        <v>12.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>-27.6</v>
+        <v>10.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>-73</v>
+        <v>27.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>-67.5</v>
+        <v>25.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>-69</v>
+        <v>25.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>-78.59999999999999</v>
+        <v>29.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>-20.4</v>
+        <v>7.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>-19.7</v>
+        <v>7.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>-33.6</v>
+        <v>12.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>-30.4</v>
+        <v>11.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>-34.2</v>
+        <v>12.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>-29.6</v>
+        <v>11.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-21.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AK15" t="n">
-        <v>-27</v>
+        <v>10.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>-16</v>
+        <v>6</v>
       </c>
       <c r="AM15" t="n">
-        <v>-22.4</v>
+        <v>8.4</v>
       </c>
       <c r="AN15" t="n">
-        <v>-25.6</v>
+        <v>9.6</v>
       </c>
       <c r="AO15" t="n">
-        <v>-28.2</v>
+        <v>10.6</v>
       </c>
       <c r="AP15" t="n">
-        <v>-73.7</v>
+        <v>27.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-94.2</v>
+        <v>35.3</v>
       </c>
       <c r="AR15" t="n">
-        <v>-140.5</v>
+        <v>52.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>-167.9</v>
+        <v>62.9</v>
       </c>
       <c r="AT15" t="n">
-        <v>-168.4</v>
+        <v>63.1</v>
       </c>
       <c r="AU15" t="n">
-        <v>-288.1</v>
+        <v>108.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>-309</v>
+        <v>115.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>-297.7</v>
+        <v>111.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MP20101010000</t>
+          <t>MP10301010000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Staff Costs</t>
+          <t>Insurance Manufacturing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Direct Costs</t>
+          <t>Net Insurance Revenue</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Total Direct Cost</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3200,133 +3200,133 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>-20.7</v>
+        <v>7.8</v>
       </c>
       <c r="O16" t="n">
-        <v>-19.1</v>
+        <v>7.2</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.2</v>
+        <v>6.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>-21.3</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>-18.6</v>
+        <v>7</v>
       </c>
       <c r="S16" t="n">
-        <v>-15.3</v>
+        <v>5.8</v>
       </c>
       <c r="T16" t="n">
-        <v>-16.1</v>
+        <v>6</v>
       </c>
       <c r="U16" t="n">
-        <v>-18.4</v>
+        <v>6.9</v>
       </c>
       <c r="V16" t="n">
-        <v>-18</v>
+        <v>6.7</v>
       </c>
       <c r="W16" t="n">
-        <v>-19</v>
+        <v>7.1</v>
       </c>
       <c r="X16" t="n">
-        <v>-18.4</v>
+        <v>6.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>-19</v>
+        <v>7.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>-57</v>
+        <v>21.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>-55.2</v>
+        <v>20.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>-52.5</v>
+        <v>19.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>-56.4</v>
+        <v>21.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>-17.1</v>
+        <v>6.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>-13</v>
+        <v>4.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>-19.1</v>
+        <v>7.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>-21.5</v>
+        <v>8</v>
       </c>
       <c r="AH16" t="n">
-        <v>-19.2</v>
+        <v>7.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>-16.9</v>
+        <v>6.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-19.2</v>
+        <v>7.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>-14</v>
+        <v>5.3</v>
       </c>
       <c r="AL16" t="n">
-        <v>-10.6</v>
+        <v>4</v>
       </c>
       <c r="AM16" t="n">
-        <v>-17.8</v>
+        <v>6.7</v>
       </c>
       <c r="AN16" t="n">
-        <v>-14.2</v>
+        <v>5.3</v>
       </c>
       <c r="AO16" t="n">
-        <v>-20.3</v>
+        <v>7.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>-49.2</v>
+        <v>18.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-57.6</v>
+        <v>21.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>-112.2</v>
+        <v>42.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>-106.8</v>
+        <v>40</v>
       </c>
       <c r="AT16" t="n">
-        <v>-109.2</v>
+        <v>40.9</v>
       </c>
       <c r="AU16" t="n">
-        <v>-221.1</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>-202.9</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AW16" t="n">
-        <v>-216.6</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MP20101010000</t>
+          <t>MP10301010000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Staff Costs</t>
+          <t>Insurance Manufacturing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Direct Costs</t>
+          <t>Net Insurance Revenue</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Total Direct Cost</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3375,133 +3375,133 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>-20.1</v>
+        <v>7.5</v>
       </c>
       <c r="O17" t="n">
-        <v>-15.8</v>
+        <v>5.9</v>
       </c>
       <c r="P17" t="n">
-        <v>-18.4</v>
+        <v>6.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>-24</v>
+        <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>-23.9</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
-        <v>-22.5</v>
+        <v>8.4</v>
       </c>
       <c r="T17" t="n">
-        <v>-28.2</v>
+        <v>10.6</v>
       </c>
       <c r="U17" t="n">
-        <v>-24.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-21.6</v>
+        <v>8.1</v>
       </c>
       <c r="W17" t="n">
-        <v>-24.3</v>
+        <v>9.1</v>
       </c>
       <c r="X17" t="n">
-        <v>-28.9</v>
+        <v>10.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>-26</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z17" t="n">
-        <v>-54.3</v>
+        <v>20.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>-70.40000000000001</v>
+        <v>26.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>-74.59999999999999</v>
+        <v>28</v>
       </c>
       <c r="AC17" t="n">
-        <v>-79.2</v>
+        <v>29.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>-28.6</v>
+        <v>10.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>-19.4</v>
+        <v>7.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>-23.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG17" t="n">
-        <v>-27.3</v>
+        <v>10.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>-22.9</v>
+        <v>8.6</v>
       </c>
       <c r="AI17" t="n">
-        <v>-28.8</v>
+        <v>10.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-26.7</v>
+        <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>-28.1</v>
+        <v>10.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>-23.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AM17" t="n">
-        <v>-35.2</v>
+        <v>13.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>-29.5</v>
+        <v>11.1</v>
       </c>
       <c r="AO17" t="n">
-        <v>-23.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AP17" t="n">
-        <v>-71.5</v>
+        <v>26.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-79</v>
+        <v>29.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>-124.7</v>
+        <v>46.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>-150.5</v>
+        <v>56.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>-145.9</v>
+        <v>54.7</v>
       </c>
       <c r="AU17" t="n">
-        <v>-278.5</v>
+        <v>104.3</v>
       </c>
       <c r="AV17" t="n">
-        <v>-316.4</v>
+        <v>118.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>-337</v>
+        <v>126.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MP20101010000</t>
+          <t>MP10301010000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Staff Costs</t>
+          <t>Insurance Manufacturing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Direct Costs</t>
+          <t>Net Insurance Revenue</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Total Direct Cost</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3550,133 +3550,133 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>-25.4</v>
+        <v>9.5</v>
       </c>
       <c r="O18" t="n">
-        <v>-21.3</v>
+        <v>8</v>
       </c>
       <c r="P18" t="n">
-        <v>-16.3</v>
+        <v>6.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>-22.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>-22.8</v>
+        <v>8.5</v>
       </c>
       <c r="S18" t="n">
-        <v>-26.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-24.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-21.4</v>
+        <v>8</v>
       </c>
       <c r="V18" t="n">
-        <v>-24.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>-23.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-22.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>-21.5</v>
+        <v>8.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>-63</v>
+        <v>23.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>-71</v>
+        <v>26.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>-70.90000000000001</v>
+        <v>26.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-67.2</v>
+        <v>25.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>-20.3</v>
+        <v>7.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>-24.2</v>
+        <v>9.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>-16.8</v>
+        <v>6.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>-18.6</v>
+        <v>7</v>
       </c>
       <c r="AH18" t="n">
-        <v>-21.3</v>
+        <v>8</v>
       </c>
       <c r="AI18" t="n">
-        <v>-15.1</v>
+        <v>5.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-19.4</v>
+        <v>7.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>-12.8</v>
+        <v>4.8</v>
       </c>
       <c r="AL18" t="n">
-        <v>-18.4</v>
+        <v>6.9</v>
       </c>
       <c r="AM18" t="n">
-        <v>-23.7</v>
+        <v>8.9</v>
       </c>
       <c r="AN18" t="n">
-        <v>-23.7</v>
+        <v>8.9</v>
       </c>
       <c r="AO18" t="n">
-        <v>-21.1</v>
+        <v>7.9</v>
       </c>
       <c r="AP18" t="n">
-        <v>-61.3</v>
+        <v>23</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-55</v>
+        <v>20.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>-134</v>
+        <v>50.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>-116.3</v>
+        <v>43.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>-119.4</v>
+        <v>44.9</v>
       </c>
       <c r="AU18" t="n">
-        <v>-272.1</v>
+        <v>101.9</v>
       </c>
       <c r="AV18" t="n">
-        <v>-235.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AW18" t="n">
-        <v>-240.1</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MP20201010000</t>
+          <t>MP20101010000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recharges</t>
+          <t>Staff Costs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indirect Costs</t>
+          <t>Direct Costs</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Total Indirect Costs (incl InterCo)</t>
+          <t>Total Direct Cost</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3725,133 +3725,133 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>-10.6</v>
+        <v>-21.2</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.2</v>
+        <v>-14.4</v>
       </c>
       <c r="P19" t="n">
-        <v>-8.4</v>
+        <v>-16.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.5</v>
+        <v>-11.1</v>
       </c>
       <c r="R19" t="n">
-        <v>-10.1</v>
+        <v>-20.2</v>
       </c>
       <c r="S19" t="n">
-        <v>-10.3</v>
+        <v>-20.7</v>
       </c>
       <c r="T19" t="n">
-        <v>-5.4</v>
+        <v>-10.8</v>
       </c>
       <c r="U19" t="n">
-        <v>-8.6</v>
+        <v>-17.2</v>
       </c>
       <c r="V19" t="n">
-        <v>-9.800000000000001</v>
+        <v>-19.6</v>
       </c>
       <c r="W19" t="n">
-        <v>-5.6</v>
+        <v>-11.3</v>
       </c>
       <c r="X19" t="n">
-        <v>-5.5</v>
+        <v>-11.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>-6.9</v>
+        <v>-13.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>-26.2</v>
+        <v>-52.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>-25.9</v>
+        <v>-52</v>
       </c>
       <c r="AB19" t="n">
-        <v>-23.8</v>
+        <v>-47.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>-18</v>
+        <v>-36.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>-8.6</v>
+        <v>-17.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>-7.2</v>
+        <v>-14.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>-9.699999999999999</v>
+        <v>-19.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>-10.1</v>
+        <v>-20.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>-10.8</v>
+        <v>-21.6</v>
       </c>
       <c r="AI19" t="n">
-        <v>-10.9</v>
+        <v>-21.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-12.3</v>
+        <v>-24.6</v>
       </c>
       <c r="AK19" t="n">
-        <v>-11.7</v>
+        <v>-23.4</v>
       </c>
       <c r="AL19" t="n">
-        <v>-7.4</v>
+        <v>-14.8</v>
       </c>
       <c r="AM19" t="n">
-        <v>-8.800000000000001</v>
+        <v>-17.6</v>
       </c>
       <c r="AN19" t="n">
-        <v>-7.8</v>
+        <v>-15.7</v>
       </c>
       <c r="AO19" t="n">
-        <v>-7.8</v>
+        <v>-15.6</v>
       </c>
       <c r="AP19" t="n">
-        <v>-25.5</v>
+        <v>-51.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-31.8</v>
+        <v>-63.7</v>
       </c>
       <c r="AR19" t="n">
-        <v>-52.1</v>
+        <v>-104.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>-57.3</v>
+        <v>-114.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>-57.2</v>
+        <v>-114.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>-93.90000000000001</v>
+        <v>-188.1</v>
       </c>
       <c r="AV19" t="n">
-        <v>-113.1</v>
+        <v>-226.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>-105.2</v>
+        <v>-210.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MP20201010000</t>
+          <t>MP20101010000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recharges</t>
+          <t>Staff Costs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indirect Costs</t>
+          <t>Direct Costs</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Total Indirect Costs (incl InterCo)</t>
+          <t>Total Direct Cost</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3900,133 +3900,133 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>-10.6</v>
+        <v>-21.3</v>
       </c>
       <c r="O20" t="n">
-        <v>-14.1</v>
+        <v>-28.2</v>
       </c>
       <c r="P20" t="n">
-        <v>-13.6</v>
+        <v>-27.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>-13.3</v>
+        <v>-26.5</v>
       </c>
       <c r="R20" t="n">
-        <v>-14</v>
+        <v>-27.9</v>
       </c>
       <c r="S20" t="n">
-        <v>-12</v>
+        <v>-24</v>
       </c>
       <c r="T20" t="n">
-        <v>-16.1</v>
+        <v>-32.3</v>
       </c>
       <c r="U20" t="n">
-        <v>-15.1</v>
+        <v>-30.3</v>
       </c>
       <c r="V20" t="n">
-        <v>-13.9</v>
+        <v>-27.8</v>
       </c>
       <c r="W20" t="n">
-        <v>-12.2</v>
+        <v>-24.5</v>
       </c>
       <c r="X20" t="n">
-        <v>-13.7</v>
+        <v>-27.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>-6.4</v>
+        <v>-12.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>-38.3</v>
+        <v>-76.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>-39.3</v>
+        <v>-78.40000000000001</v>
       </c>
       <c r="AB20" t="n">
-        <v>-45.1</v>
+        <v>-90.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-32.3</v>
+        <v>-64.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>-12.7</v>
+        <v>-25.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>-15.6</v>
+        <v>-31.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>-11.2</v>
+        <v>-22.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>-16</v>
+        <v>-32</v>
       </c>
       <c r="AH20" t="n">
-        <v>-15.9</v>
+        <v>-31.7</v>
       </c>
       <c r="AI20" t="n">
-        <v>-11.5</v>
+        <v>-23.1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-14.7</v>
+        <v>-29.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>-14.6</v>
+        <v>-29.1</v>
       </c>
       <c r="AL20" t="n">
-        <v>-16.7</v>
+        <v>-33.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>-17.2</v>
+        <v>-34.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>-15.3</v>
+        <v>-30.7</v>
       </c>
       <c r="AO20" t="n">
-        <v>-13</v>
+        <v>-26.1</v>
       </c>
       <c r="AP20" t="n">
-        <v>-39.5</v>
+        <v>-78.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-43.4</v>
+        <v>-86.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>-77.59999999999999</v>
+        <v>-155.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>-82.90000000000001</v>
+        <v>-165.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>-83.59999999999999</v>
+        <v>-166.9</v>
       </c>
       <c r="AU20" t="n">
-        <v>-155</v>
+        <v>-310.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>-174.4</v>
+        <v>-348.9</v>
       </c>
       <c r="AW20" t="n">
-        <v>-162.5</v>
+        <v>-325.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MP20201010000</t>
+          <t>MP20101010000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Recharges</t>
+          <t>Staff Costs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indirect Costs</t>
+          <t>Direct Costs</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Total Indirect Costs (incl InterCo)</t>
+          <t>Total Direct Cost</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4075,133 +4075,133 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>-7.6</v>
+        <v>-15.1</v>
       </c>
       <c r="O21" t="n">
-        <v>-6.4</v>
+        <v>-12.9</v>
       </c>
       <c r="P21" t="n">
-        <v>-8.199999999999999</v>
+        <v>-16.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>-7.5</v>
+        <v>-15.1</v>
       </c>
       <c r="R21" t="n">
-        <v>-6.9</v>
+        <v>-13.7</v>
       </c>
       <c r="S21" t="n">
-        <v>-8.6</v>
+        <v>-17.3</v>
       </c>
       <c r="T21" t="n">
-        <v>-8</v>
+        <v>-15.9</v>
       </c>
       <c r="U21" t="n">
+        <v>-18</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-25.9</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-44.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-46.1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-53.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-58.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-21.3</v>
+      </c>
+      <c r="AG21" t="n">
         <v>-9</v>
       </c>
-      <c r="V21" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-12.9</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>-22.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>-23</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-26.8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>-29.3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>-4.5</v>
-      </c>
       <c r="AH21" t="n">
-        <v>-7.3</v>
+        <v>-14.7</v>
       </c>
       <c r="AI21" t="n">
-        <v>-9.1</v>
+        <v>-18.2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-9.699999999999999</v>
+        <v>-19.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>-12.8</v>
+        <v>-25.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>-9.199999999999999</v>
+        <v>-18.5</v>
       </c>
       <c r="AM21" t="n">
-        <v>-10.9</v>
+        <v>-21.9</v>
       </c>
       <c r="AN21" t="n">
-        <v>-10</v>
+        <v>-20.1</v>
       </c>
       <c r="AO21" t="n">
-        <v>-10.4</v>
+        <v>-20.7</v>
       </c>
       <c r="AP21" t="n">
-        <v>-30.1</v>
+        <v>-60.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>-20.9</v>
+        <v>-41.9</v>
       </c>
       <c r="AR21" t="n">
-        <v>-45.2</v>
+        <v>-90.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>-51</v>
+        <v>-102.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>-53.8</v>
+        <v>-107.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>-101.3</v>
+        <v>-202.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>-114</v>
+        <v>-228.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>-108.1</v>
+        <v>-216.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MP20201010000</t>
+          <t>MP20101010000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recharges</t>
+          <t>Staff Costs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indirect Costs</t>
+          <t>Direct Costs</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Total Indirect Costs (incl InterCo)</t>
+          <t>Total Direct Cost</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4250,133 +4250,133 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>-17.7</v>
+        <v>-35.4</v>
       </c>
       <c r="O22" t="n">
-        <v>-11.4</v>
+        <v>-22.8</v>
       </c>
       <c r="P22" t="n">
-        <v>-15</v>
+        <v>-30</v>
       </c>
       <c r="Q22" t="n">
-        <v>-20.4</v>
+        <v>-40.7</v>
       </c>
       <c r="R22" t="n">
-        <v>-13.7</v>
+        <v>-27.3</v>
       </c>
       <c r="S22" t="n">
-        <v>-14.4</v>
+        <v>-28.7</v>
       </c>
       <c r="T22" t="n">
-        <v>-17.6</v>
+        <v>-35.3</v>
       </c>
       <c r="U22" t="n">
-        <v>-14.4</v>
+        <v>-28.8</v>
       </c>
       <c r="V22" t="n">
-        <v>-12</v>
+        <v>-24</v>
       </c>
       <c r="W22" t="n">
-        <v>-15</v>
+        <v>-30.1</v>
       </c>
       <c r="X22" t="n">
-        <v>-16</v>
+        <v>-31.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>-16.3</v>
+        <v>-32.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>-44.1</v>
+        <v>-88.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>-48.5</v>
+        <v>-96.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>-44</v>
+        <v>-88.09999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>-47.3</v>
+        <v>-94.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>-12.6</v>
+        <v>-25.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>-19.8</v>
+        <v>-39.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>-19.6</v>
+        <v>-39.2</v>
       </c>
       <c r="AG22" t="n">
-        <v>-14.9</v>
+        <v>-29.8</v>
       </c>
       <c r="AH22" t="n">
-        <v>-15.6</v>
+        <v>-31.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>-13.6</v>
+        <v>-27.2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-18.9</v>
+        <v>-37.8</v>
       </c>
       <c r="AK22" t="n">
-        <v>-12.8</v>
+        <v>-25.6</v>
       </c>
       <c r="AL22" t="n">
-        <v>-16.8</v>
+        <v>-33.5</v>
       </c>
       <c r="AM22" t="n">
-        <v>-13.5</v>
+        <v>-26.9</v>
       </c>
       <c r="AN22" t="n">
-        <v>-12.8</v>
+        <v>-25.7</v>
       </c>
       <c r="AO22" t="n">
-        <v>-16.9</v>
+        <v>-33.8</v>
       </c>
       <c r="AP22" t="n">
-        <v>-52</v>
+        <v>-104.1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-44.1</v>
+        <v>-88.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>-92.59999999999999</v>
+        <v>-184.9</v>
       </c>
       <c r="AS22" t="n">
-        <v>-96.09999999999999</v>
+        <v>-192.3</v>
       </c>
       <c r="AT22" t="n">
-        <v>-101.9</v>
+        <v>-203.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>-183.9</v>
+        <v>-367.7</v>
       </c>
       <c r="AV22" t="n">
-        <v>-187.8</v>
+        <v>-375.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>-190.1</v>
+        <v>-380.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MP30101010000</t>
+          <t>MP20201010000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ECL Charge</t>
+          <t>Recharges</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>Indirect Costs</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Expected credit losses</t>
+          <t>Total Indirect Costs (incl InterCo)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4425,133 +4425,133 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>-5.4</v>
+        <v>-10.9</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.8</v>
+        <v>-11.7</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.2</v>
+        <v>-14.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>-6.7</v>
+        <v>-13.5</v>
       </c>
       <c r="R23" t="n">
-        <v>-4.9</v>
+        <v>-9.9</v>
       </c>
       <c r="S23" t="n">
+        <v>-16</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-11</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-36.9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-39.4</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-33.3</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-32.9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="AO23" t="n">
         <v>-8</v>
       </c>
-      <c r="T23" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>-18.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>-19.6</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-16.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>-4</v>
-      </c>
       <c r="AP23" t="n">
-        <v>-15.3</v>
+        <v>-30.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>-15.8</v>
+        <v>-31.6</v>
       </c>
       <c r="AR23" t="n">
-        <v>-38</v>
+        <v>-76.3</v>
       </c>
       <c r="AS23" t="n">
-        <v>-31.1</v>
+        <v>-62.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>-30.3</v>
+        <v>-60.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>-71.2</v>
+        <v>-142.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>-61.4</v>
+        <v>-122.8</v>
       </c>
       <c r="AW23" t="n">
-        <v>-57.5</v>
+        <v>-115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MP30101010000</t>
+          <t>MP20201010000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ECL Charge</t>
+          <t>Recharges</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>Indirect Costs</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Expected credit losses</t>
+          <t>Total Indirect Costs (incl InterCo)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4600,133 +4600,133 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.8</v>
+        <v>-15.6</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.8</v>
+        <v>-13.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>-9.9</v>
+        <v>-19.8</v>
       </c>
       <c r="R24" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-13</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-14</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-16</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-41.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-51.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-38.9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-46.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-22.7</v>
+      </c>
+      <c r="AI24" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="S24" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-7</v>
-      </c>
-      <c r="X24" t="n">
-        <v>-8</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>-20.8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>-26</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>-23.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>-11.4</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>-4.3</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>-6.4</v>
+        <v>-12.7</v>
       </c>
       <c r="AK24" t="n">
-        <v>-7.4</v>
+        <v>-14.8</v>
       </c>
       <c r="AL24" t="n">
-        <v>-7.4</v>
+        <v>-14.8</v>
       </c>
       <c r="AM24" t="n">
-        <v>-7.8</v>
+        <v>-15.5</v>
       </c>
       <c r="AN24" t="n">
-        <v>-6.8</v>
+        <v>-13.6</v>
       </c>
       <c r="AO24" t="n">
-        <v>-7.7</v>
+        <v>-15.4</v>
       </c>
       <c r="AP24" t="n">
-        <v>-24.4</v>
+        <v>-48.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-22.9</v>
+        <v>-45.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>-46.8</v>
+        <v>-93.40000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>-47.3</v>
+        <v>-94.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>-45.8</v>
+        <v>-91.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>-89.5</v>
+        <v>-178.9</v>
       </c>
       <c r="AV24" t="n">
-        <v>-90.8</v>
+        <v>-181.3</v>
       </c>
       <c r="AW24" t="n">
-        <v>-87.7</v>
+        <v>-175.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MP30101010000</t>
+          <t>MP20201010000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ECL Charge</t>
+          <t>Recharges</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>Indirect Costs</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Expected credit losses</t>
+          <t>Total Indirect Costs (incl InterCo)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4775,133 +4775,133 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>-6.2</v>
+        <v>-12.5</v>
       </c>
       <c r="O25" t="n">
-        <v>-5</v>
+        <v>-9.9</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.9</v>
+        <v>-9.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>-7</v>
+        <v>-14.1</v>
       </c>
       <c r="R25" t="n">
-        <v>-5.4</v>
+        <v>-10.9</v>
       </c>
       <c r="S25" t="n">
-        <v>-7</v>
+        <v>-14.1</v>
       </c>
       <c r="T25" t="n">
-        <v>-7.2</v>
+        <v>-14.4</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.6</v>
+        <v>-13.3</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.9</v>
+        <v>-13.8</v>
       </c>
       <c r="W25" t="n">
-        <v>-6.1</v>
+        <v>-12.2</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.5</v>
+        <v>-9</v>
       </c>
       <c r="Y25" t="n">
-        <v>-6.2</v>
+        <v>-12.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>-16.1</v>
+        <v>-32.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>-19.4</v>
+        <v>-39.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>-20.7</v>
+        <v>-41.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-16.8</v>
+        <v>-33.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>-7.6</v>
+        <v>-15.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>-6.4</v>
+        <v>-12.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>-6.9</v>
+        <v>-13.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>-8</v>
+        <v>-15.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>-5.9</v>
+        <v>-11.9</v>
       </c>
       <c r="AI25" t="n">
-        <v>-7.8</v>
+        <v>-15.7</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-9.4</v>
+        <v>-18.7</v>
       </c>
       <c r="AK25" t="n">
-        <v>-6.3</v>
+        <v>-12.7</v>
       </c>
       <c r="AL25" t="n">
-        <v>-7.2</v>
+        <v>-14.4</v>
       </c>
       <c r="AM25" t="n">
-        <v>-6.8</v>
+        <v>-13.7</v>
       </c>
       <c r="AN25" t="n">
-        <v>-9</v>
+        <v>-17.9</v>
       </c>
       <c r="AO25" t="n">
-        <v>-7.4</v>
+        <v>-14.8</v>
       </c>
       <c r="AP25" t="n">
-        <v>-20.9</v>
+        <v>-41.7</v>
       </c>
       <c r="AQ25" t="n">
-        <v>-21.7</v>
+        <v>-43.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>-35.5</v>
+        <v>-71.40000000000001</v>
       </c>
       <c r="AS25" t="n">
-        <v>-42.6</v>
+        <v>-85.2</v>
       </c>
       <c r="AT25" t="n">
-        <v>-44.6</v>
+        <v>-89.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>-73</v>
+        <v>-146.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>-88.7</v>
+        <v>-177.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>-88.40000000000001</v>
+        <v>-176.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MP30101010000</t>
+          <t>MP20201010000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ECL Charge</t>
+          <t>Recharges</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>Indirect Costs</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Expected credit losses</t>
+          <t>Total Indirect Costs (incl InterCo)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4950,133 +4950,133 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>-4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.1</v>
+        <v>-16.3</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.4</v>
+        <v>-14.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.1</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>-7.3</v>
+        <v>-14.5</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.1</v>
+        <v>-12.3</v>
       </c>
       <c r="T26" t="n">
-        <v>-6.9</v>
+        <v>-13.8</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.8</v>
+        <v>-13.6</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.4</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>-6</v>
+        <v>-12.1</v>
       </c>
       <c r="X26" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-39.3</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-36.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-39.7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AE26" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="Y26" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>-19.6</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>-18.1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>-19.8</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>-4.1</v>
-      </c>
       <c r="AF26" t="n">
-        <v>-4.3</v>
+        <v>-8.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>-6.2</v>
+        <v>-12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>-7.9</v>
+        <v>-15.9</v>
       </c>
       <c r="AI26" t="n">
-        <v>-6.4</v>
+        <v>-12.7</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-6.1</v>
+        <v>-12.2</v>
       </c>
       <c r="AK26" t="n">
-        <v>-8.6</v>
+        <v>-17.3</v>
       </c>
       <c r="AL26" t="n">
-        <v>-5.2</v>
+        <v>-10.3</v>
       </c>
       <c r="AM26" t="n">
-        <v>-5</v>
+        <v>-9.9</v>
       </c>
       <c r="AN26" t="n">
-        <v>-6.5</v>
+        <v>-13</v>
       </c>
       <c r="AO26" t="n">
-        <v>-6.5</v>
+        <v>-13</v>
       </c>
       <c r="AP26" t="n">
-        <v>-12.9</v>
+        <v>-25.7</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-20.5</v>
+        <v>-41.1</v>
       </c>
       <c r="AR26" t="n">
-        <v>-37.1</v>
+        <v>-74.3</v>
       </c>
       <c r="AS26" t="n">
-        <v>-33.4</v>
+        <v>-66.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>-33.9</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="AU26" t="n">
-        <v>-75</v>
+        <v>-150.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>-71.3</v>
+        <v>-142.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>-73.3</v>
+        <v>-146.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MP40101010000</t>
+          <t>MP30101010000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JV Share</t>
+          <t>ECL Charge</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Associates</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Share of Profit in Associates &amp; JV's</t>
+          <t>Expected credit losses</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5125,133 +5125,133 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>-3.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.5</v>
+        <v>-4.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.4</v>
+        <v>-4.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.7</v>
+        <v>-5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="S27" t="n">
-        <v>1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.4</v>
+        <v>-4.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.9</v>
+        <v>-5.6</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>-5.9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>-4.3</v>
       </c>
       <c r="X27" t="n">
-        <v>1.8</v>
+        <v>-5.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>-3.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>4</v>
+        <v>-11.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.7</v>
+        <v>-14</v>
       </c>
       <c r="AB27" t="n">
-        <v>5.3</v>
+        <v>-15.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.5</v>
+        <v>-13.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.5</v>
+        <v>-4.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.7</v>
+        <v>-5</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>-5.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>-4</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1</v>
+        <v>-2.9</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.4</v>
+        <v>-4.3</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.2</v>
+        <v>-3.7</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.6</v>
+        <v>-4.7</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.8</v>
+        <v>-2.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.1</v>
+        <v>-15.1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.2</v>
+        <v>-12.7</v>
       </c>
       <c r="AR27" t="n">
-        <v>8.699999999999999</v>
+        <v>-25.9</v>
       </c>
       <c r="AS27" t="n">
-        <v>9.300000000000001</v>
+        <v>-27.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>-26.9</v>
       </c>
       <c r="AU27" t="n">
-        <v>18.5</v>
+        <v>-55.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>16.4</v>
+        <v>-49.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>15.3</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MP40101010000</t>
+          <t>MP30101010000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JV Share</t>
+          <t>ECL Charge</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Associates</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Share of Profit in Associates &amp; JV's</t>
+          <t>Expected credit losses</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5300,133 +5300,133 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.7</v>
+        <v>-5.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.6</v>
+        <v>-4.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>-5.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.2</v>
+        <v>-3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.6</v>
+        <v>-4.7</v>
       </c>
       <c r="S28" t="n">
-        <v>1.8</v>
+        <v>-5.4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>-6.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.7</v>
+        <v>-5.2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.9</v>
+        <v>-5.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.6</v>
+        <v>-4.7</v>
       </c>
       <c r="X28" t="n">
-        <v>1.9</v>
+        <v>-5.7</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.4</v>
+        <v>-7.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.3</v>
+        <v>-15.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.6</v>
+        <v>-13.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>5.7</v>
+        <v>-17.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.9</v>
+        <v>-17.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>-4.8</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.7</v>
+        <v>-8.1</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.6</v>
+        <v>-4.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.8</v>
+        <v>-5.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.9</v>
+        <v>-5.7</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.2</v>
+        <v>-6.6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.1</v>
+        <v>-3.2</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.1</v>
+        <v>-6.2</v>
       </c>
       <c r="AM28" t="n">
-        <v>2.1</v>
+        <v>-6.4</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.1</v>
+        <v>-6.2</v>
       </c>
       <c r="AO28" t="n">
-        <v>2.8</v>
+        <v>-8.4</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.9</v>
+        <v>-17.7</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.9</v>
+        <v>-17.8</v>
       </c>
       <c r="AR28" t="n">
-        <v>9.9</v>
+        <v>-29.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>11.8</v>
+        <v>-35.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>11.3</v>
+        <v>-34</v>
       </c>
       <c r="AU28" t="n">
-        <v>21.5</v>
+        <v>-64.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>23.4</v>
+        <v>-70.09999999999999</v>
       </c>
       <c r="AW28" t="n">
-        <v>21.9</v>
+        <v>-65.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MP40101010000</t>
+          <t>MP30101010000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JV Share</t>
+          <t>ECL Charge</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Associates</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Share of Profit in Associates &amp; JV's</t>
+          <t>Expected credit losses</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5475,133 +5475,133 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>-5.9</v>
       </c>
       <c r="O29" t="n">
-        <v>1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="P29" t="n">
-        <v>1.4</v>
+        <v>-4.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5</v>
+        <v>-1.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.7</v>
+        <v>-5.1</v>
       </c>
       <c r="S29" t="n">
-        <v>1.4</v>
+        <v>-4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.7</v>
+        <v>-5.2</v>
       </c>
       <c r="U29" t="n">
-        <v>2.1</v>
+        <v>-6.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.5</v>
+        <v>-4.4</v>
       </c>
       <c r="W29" t="n">
-        <v>1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="X29" t="n">
-        <v>1.3</v>
+        <v>-4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>-3.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.5</v>
+        <v>-13.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.6</v>
+        <v>-10.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>5.3</v>
+        <v>-15.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>-11.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.3</v>
+        <v>-3.9</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.7</v>
+        <v>-5</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>-4.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.8</v>
+        <v>-5.3</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.6</v>
+        <v>-4.9</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.4</v>
+        <v>-4.3</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.7</v>
+        <v>-5</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.4</v>
+        <v>-4.3</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.1</v>
+        <v>-3.4</v>
       </c>
       <c r="AO29" t="n">
-        <v>1.9</v>
+        <v>-5.7</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.5</v>
+        <v>-13.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.7</v>
+        <v>-14.1</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.1</v>
+        <v>-23.9</v>
       </c>
       <c r="AS29" t="n">
-        <v>9.199999999999999</v>
+        <v>-27.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>9.6</v>
+        <v>-28.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>17.3</v>
+        <v>-51.7</v>
       </c>
       <c r="AV29" t="n">
-        <v>18.3</v>
+        <v>-55.1</v>
       </c>
       <c r="AW29" t="n">
-        <v>18.1</v>
+        <v>-54.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MP40101010000</t>
+          <t>MP30101010000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JV Share</t>
+          <t>ECL Charge</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Associates</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Share of Profit in Associates &amp; JV's</t>
+          <t>Expected credit losses</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5650,133 +5650,133 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.9</v>
+        <v>-5.8</v>
       </c>
       <c r="P30" t="n">
-        <v>1.6</v>
+        <v>-4.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.7</v>
+        <v>-5.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>-4.6</v>
       </c>
       <c r="S30" t="n">
-        <v>1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.7</v>
+        <v>-5.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.5</v>
+        <v>-4.4</v>
       </c>
       <c r="W30" t="n">
-        <v>1.4</v>
+        <v>-4.1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.6</v>
+        <v>-4.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.5</v>
+        <v>-4.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.5</v>
+        <v>-13.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.6</v>
+        <v>-14</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.2</v>
+        <v>-12.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.5</v>
+        <v>-13.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.7</v>
+        <v>-5.1</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.9</v>
+        <v>-2.6</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>-4.1</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.7</v>
+        <v>-5.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.9</v>
+        <v>-5.7</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.5</v>
+        <v>-4.4</v>
       </c>
       <c r="AM30" t="n">
-        <v>2</v>
+        <v>-5.9</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="AO30" t="n">
-        <v>1.7</v>
+        <v>-5.1</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.6</v>
+        <v>-13.8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4</v>
+        <v>-11.8</v>
       </c>
       <c r="AR30" t="n">
-        <v>9.1</v>
+        <v>-27.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>8.6</v>
+        <v>-25.6</v>
       </c>
       <c r="AT30" t="n">
-        <v>8.1</v>
+        <v>-24.1</v>
       </c>
       <c r="AU30" t="n">
-        <v>17.8</v>
+        <v>-53.3</v>
       </c>
       <c r="AV30" t="n">
-        <v>18.5</v>
+        <v>-55.1</v>
       </c>
       <c r="AW30" t="n">
-        <v>19.2</v>
+        <v>-57.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MP90101010000</t>
+          <t>MP40101010000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deposits balance</t>
+          <t>JV Share</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deposits</t>
+          <t>Associates</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Customer Deposits</t>
+          <t>Share of Profit in Associates &amp; JV's</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5825,133 +5825,133 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1154.8</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>1092.8</v>
+        <v>2.5</v>
       </c>
       <c r="P31" t="n">
-        <v>1106.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>1123.2</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
-        <v>1155.7</v>
+        <v>3.7</v>
       </c>
       <c r="S31" t="n">
-        <v>1155.5</v>
+        <v>2.2</v>
       </c>
       <c r="T31" t="n">
-        <v>1117.2</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1108.1</v>
+        <v>2.7</v>
       </c>
       <c r="V31" t="n">
-        <v>1120.2</v>
+        <v>2</v>
       </c>
       <c r="W31" t="n">
-        <v>1124.4</v>
+        <v>2.7</v>
       </c>
       <c r="X31" t="n">
-        <v>1153.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>1103.5</v>
+        <v>2.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>1106.9</v>
+        <v>7.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>1155.5</v>
+        <v>9</v>
       </c>
       <c r="AB31" t="n">
-        <v>1120.2</v>
+        <v>6.9</v>
       </c>
       <c r="AC31" t="n">
-        <v>1103.5</v>
+        <v>7.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>1220.7</v>
+        <v>2.9</v>
       </c>
       <c r="AE31" t="n">
-        <v>1216.1</v>
+        <v>1.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>1222.1</v>
+        <v>3</v>
       </c>
       <c r="AG31" t="n">
-        <v>1218.5</v>
+        <v>1.9</v>
       </c>
       <c r="AH31" t="n">
-        <v>1206.6</v>
+        <v>2.3</v>
       </c>
       <c r="AI31" t="n">
-        <v>1186.5</v>
+        <v>2.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1180.7</v>
+        <v>2.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>1167.6</v>
+        <v>3.1</v>
       </c>
       <c r="AL31" t="n">
-        <v>1165.4</v>
+        <v>2.7</v>
       </c>
       <c r="AM31" t="n">
-        <v>1202.7</v>
+        <v>2.5</v>
       </c>
       <c r="AN31" t="n">
-        <v>1186.4</v>
+        <v>2.9</v>
       </c>
       <c r="AO31" t="n">
-        <v>1233.5</v>
+        <v>3.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1222.1</v>
+        <v>7.8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1186.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR31" t="n">
-        <v>1155.5</v>
+        <v>16.7</v>
       </c>
       <c r="AS31" t="n">
-        <v>1186.5</v>
+        <v>14.4</v>
       </c>
       <c r="AT31" t="n">
-        <v>1211.4</v>
+        <v>14</v>
       </c>
       <c r="AU31" t="n">
-        <v>1103.5</v>
+        <v>31.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>1233.5</v>
+        <v>31.6</v>
       </c>
       <c r="AW31" t="n">
-        <v>1227</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MP90101010000</t>
+          <t>MP40101010000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deposits balance</t>
+          <t>JV Share</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Deposits</t>
+          <t>Associates</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Customer Deposits</t>
+          <t>Share of Profit in Associates &amp; JV's</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6000,155 +6000,155 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>761.9</v>
+        <v>1.1</v>
       </c>
       <c r="O32" t="n">
-        <v>764.4</v>
+        <v>2.2</v>
       </c>
       <c r="P32" t="n">
-        <v>767.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>772.2</v>
+        <v>0.9</v>
       </c>
       <c r="R32" t="n">
-        <v>763.9</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>739.3</v>
+        <v>1.6</v>
       </c>
       <c r="T32" t="n">
-        <v>771.9</v>
+        <v>1.7</v>
       </c>
       <c r="U32" t="n">
-        <v>747.1</v>
+        <v>1.6</v>
       </c>
       <c r="V32" t="n">
-        <v>759.5</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>750.7</v>
+        <v>1.1</v>
       </c>
       <c r="X32" t="n">
-        <v>767.3</v>
+        <v>1.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>742.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z32" t="n">
-        <v>767.7</v>
+        <v>5.4</v>
       </c>
       <c r="AA32" t="n">
-        <v>739.3</v>
+        <v>3.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>759.5</v>
+        <v>4.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>742.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>756.8</v>
+        <v>1.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>756.7</v>
+        <v>1.2</v>
       </c>
       <c r="AF32" t="n">
-        <v>752.5</v>
+        <v>1.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>786.2</v>
+        <v>1</v>
       </c>
       <c r="AH32" t="n">
-        <v>772.1</v>
+        <v>1.4</v>
       </c>
       <c r="AI32" t="n">
-        <v>760.5</v>
+        <v>1.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>791.1</v>
+        <v>1.6</v>
       </c>
       <c r="AK32" t="n">
-        <v>750.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL32" t="n">
-        <v>767.3</v>
+        <v>1.3</v>
       </c>
       <c r="AM32" t="n">
-        <v>783.2</v>
+        <v>1.4</v>
       </c>
       <c r="AN32" t="n">
-        <v>784.2</v>
+        <v>1.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>787.6</v>
+        <v>1.3</v>
       </c>
       <c r="AP32" t="n">
-        <v>752.5</v>
+        <v>3.9</v>
       </c>
       <c r="AQ32" t="n">
-        <v>760.5</v>
+        <v>3.8</v>
       </c>
       <c r="AR32" t="n">
-        <v>739.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AS32" t="n">
-        <v>760.5</v>
+        <v>7.7</v>
       </c>
       <c r="AT32" t="n">
-        <v>793.2</v>
+        <v>7.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>742.8</v>
+        <v>18.3</v>
       </c>
       <c r="AV32" t="n">
-        <v>787.6</v>
+        <v>16.1</v>
       </c>
       <c r="AW32" t="n">
-        <v>777.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MP90101010000</t>
+          <t>MP40101010000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deposits balance</t>
+          <t>JV Share</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Associates</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Share of Profit in Associates &amp; JV's</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PR05001000</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>Deposits</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Customer Deposits</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>PBT</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>PR05001000</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Current Accounts Total</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Deposits</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>Total Product</t>
@@ -6175,133 +6175,133 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1081.9</v>
+        <v>1.3</v>
       </c>
       <c r="O33" t="n">
-        <v>1116</v>
+        <v>1.5</v>
       </c>
       <c r="P33" t="n">
-        <v>1127.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>1071.7</v>
+        <v>2.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1104</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>1105.6</v>
+        <v>1.6</v>
       </c>
       <c r="T33" t="n">
-        <v>1079.1</v>
+        <v>1.7</v>
       </c>
       <c r="U33" t="n">
-        <v>1089.1</v>
+        <v>1.2</v>
       </c>
       <c r="V33" t="n">
-        <v>1074.1</v>
+        <v>1.7</v>
       </c>
       <c r="W33" t="n">
-        <v>1078.2</v>
+        <v>1.6</v>
       </c>
       <c r="X33" t="n">
-        <v>1081.6</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1104.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z33" t="n">
-        <v>1127.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>1105.6</v>
+        <v>5.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1074.1</v>
+        <v>4.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>1104.3</v>
+        <v>4.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>1133.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1103.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF33" t="n">
-        <v>1090.3</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>1111.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH33" t="n">
-        <v>1135.3</v>
+        <v>1.9</v>
       </c>
       <c r="AI33" t="n">
-        <v>1102.1</v>
+        <v>1.9</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1116.2</v>
+        <v>2.2</v>
       </c>
       <c r="AK33" t="n">
-        <v>1126.7</v>
+        <v>1.7</v>
       </c>
       <c r="AL33" t="n">
-        <v>1132.7</v>
+        <v>2.1</v>
       </c>
       <c r="AM33" t="n">
-        <v>1095.7</v>
+        <v>1.6</v>
       </c>
       <c r="AN33" t="n">
-        <v>1100.6</v>
+        <v>2</v>
       </c>
       <c r="AO33" t="n">
-        <v>1136.5</v>
+        <v>1.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>1090.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1102.1</v>
+        <v>5.6</v>
       </c>
       <c r="AR33" t="n">
-        <v>1105.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS33" t="n">
-        <v>1102.1</v>
+        <v>11</v>
       </c>
       <c r="AT33" t="n">
-        <v>1086.4</v>
+        <v>10.7</v>
       </c>
       <c r="AU33" t="n">
-        <v>1104.3</v>
+        <v>17.7</v>
       </c>
       <c r="AV33" t="n">
-        <v>1136.5</v>
+        <v>22.1</v>
       </c>
       <c r="AW33" t="n">
-        <v>1127</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MP90101010000</t>
+          <t>MP40101010000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deposits balance</t>
+          <t>JV Share</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Deposits</t>
+          <t>Associates</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Customer Deposits</t>
+          <t>Share of Profit in Associates &amp; JV's</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6350,155 +6350,155 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1087.7</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>1076.8</v>
+        <v>2.1</v>
       </c>
       <c r="P34" t="n">
-        <v>1111.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>1077.2</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1064.2</v>
+        <v>2.8</v>
       </c>
       <c r="S34" t="n">
-        <v>1123.1</v>
+        <v>2.8</v>
       </c>
       <c r="T34" t="n">
-        <v>1091.7</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1117.8</v>
+        <v>3.2</v>
       </c>
       <c r="V34" t="n">
-        <v>1090.5</v>
+        <v>2.3</v>
       </c>
       <c r="W34" t="n">
-        <v>1121.9</v>
+        <v>2.3</v>
       </c>
       <c r="X34" t="n">
-        <v>1094.1</v>
+        <v>3</v>
       </c>
       <c r="Y34" t="n">
-        <v>1074.5</v>
+        <v>2.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>1111.7</v>
+        <v>6.7</v>
       </c>
       <c r="AA34" t="n">
-        <v>1123.1</v>
+        <v>8.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>1090.5</v>
+        <v>8</v>
       </c>
       <c r="AC34" t="n">
-        <v>1074.5</v>
+        <v>7.9</v>
       </c>
       <c r="AD34" t="n">
-        <v>1223.7</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1264.2</v>
+        <v>2.1</v>
       </c>
       <c r="AF34" t="n">
-        <v>1271</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>1291.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH34" t="n">
-        <v>1229.3</v>
+        <v>2.6</v>
       </c>
       <c r="AI34" t="n">
-        <v>1269.6</v>
+        <v>1.8</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1230.8</v>
+        <v>2.6</v>
       </c>
       <c r="AK34" t="n">
-        <v>1259.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL34" t="n">
-        <v>1283.4</v>
+        <v>1.9</v>
       </c>
       <c r="AM34" t="n">
-        <v>1295.7</v>
+        <v>2.8</v>
       </c>
       <c r="AN34" t="n">
-        <v>1237.5</v>
+        <v>2.3</v>
       </c>
       <c r="AO34" t="n">
-        <v>1232.1</v>
+        <v>2.2</v>
       </c>
       <c r="AP34" t="n">
-        <v>1271</v>
+        <v>6.7</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1269.6</v>
+        <v>7.1</v>
       </c>
       <c r="AR34" t="n">
-        <v>1123.1</v>
+        <v>15.3</v>
       </c>
       <c r="AS34" t="n">
-        <v>1269.6</v>
+        <v>13.8</v>
       </c>
       <c r="AT34" t="n">
-        <v>1320.9</v>
+        <v>13.2</v>
       </c>
       <c r="AU34" t="n">
-        <v>1074.5</v>
+        <v>31.2</v>
       </c>
       <c r="AV34" t="n">
-        <v>1232.1</v>
+        <v>28.1</v>
       </c>
       <c r="AW34" t="n">
-        <v>1246.9</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MP90201010000</t>
+          <t>MP90101010000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Loans balance</t>
+          <t>Deposits balance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Customer Deposits</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PR04004001</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Wealth Lending</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>Loans</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Loan and Advances</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PBT</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>PR04004001</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Wealth Lending</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Loans</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>Total Product</t>
@@ -6525,155 +6525,155 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>972.2</v>
+        <v>841.5</v>
       </c>
       <c r="O35" t="n">
-        <v>939.8</v>
+        <v>874.4</v>
       </c>
       <c r="P35" t="n">
-        <v>950.3</v>
+        <v>841.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>975.6</v>
+        <v>854.7</v>
       </c>
       <c r="R35" t="n">
-        <v>974.7</v>
+        <v>844</v>
       </c>
       <c r="S35" t="n">
-        <v>937.6</v>
+        <v>847</v>
       </c>
       <c r="T35" t="n">
-        <v>939.6</v>
+        <v>869.9</v>
       </c>
       <c r="U35" t="n">
-        <v>950</v>
+        <v>876.7</v>
       </c>
       <c r="V35" t="n">
-        <v>956.8</v>
+        <v>844.3</v>
       </c>
       <c r="W35" t="n">
-        <v>949.1</v>
+        <v>835.8</v>
       </c>
       <c r="X35" t="n">
-        <v>934.2</v>
+        <v>862.9</v>
       </c>
       <c r="Y35" t="n">
-        <v>941.3</v>
+        <v>836.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>950.3</v>
+        <v>841.7</v>
       </c>
       <c r="AA35" t="n">
-        <v>937.6</v>
+        <v>847</v>
       </c>
       <c r="AB35" t="n">
-        <v>956.8</v>
+        <v>844.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>941.3</v>
+        <v>836.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>926.9</v>
+        <v>813.8</v>
       </c>
       <c r="AE35" t="n">
-        <v>936.4</v>
+        <v>858.9</v>
       </c>
       <c r="AF35" t="n">
-        <v>889.4</v>
+        <v>834.8</v>
       </c>
       <c r="AG35" t="n">
-        <v>918</v>
+        <v>854.8</v>
       </c>
       <c r="AH35" t="n">
-        <v>928.7</v>
+        <v>833.9</v>
       </c>
       <c r="AI35" t="n">
-        <v>889.2</v>
+        <v>857.9</v>
       </c>
       <c r="AJ35" t="n">
-        <v>910.2</v>
+        <v>818</v>
       </c>
       <c r="AK35" t="n">
-        <v>919.1</v>
+        <v>844.8</v>
       </c>
       <c r="AL35" t="n">
-        <v>910.5</v>
+        <v>832.2</v>
       </c>
       <c r="AM35" t="n">
-        <v>923.3</v>
+        <v>838.9</v>
       </c>
       <c r="AN35" t="n">
-        <v>911.6</v>
+        <v>820.8</v>
       </c>
       <c r="AO35" t="n">
-        <v>911.2</v>
+        <v>827.7</v>
       </c>
       <c r="AP35" t="n">
-        <v>889.4</v>
+        <v>834.8</v>
       </c>
       <c r="AQ35" t="n">
-        <v>889.2</v>
+        <v>857.9</v>
       </c>
       <c r="AR35" t="n">
-        <v>937.6</v>
+        <v>847</v>
       </c>
       <c r="AS35" t="n">
-        <v>889.2</v>
+        <v>857.9</v>
       </c>
       <c r="AT35" t="n">
-        <v>885.5</v>
+        <v>831.9</v>
       </c>
       <c r="AU35" t="n">
-        <v>941.3</v>
+        <v>836.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>911.2</v>
+        <v>827.7</v>
       </c>
       <c r="AW35" t="n">
-        <v>882</v>
+        <v>796.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MP90201010000</t>
+          <t>MP90101010000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Loans balance</t>
+          <t>Deposits balance</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Customer Deposits</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>Loans</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Loan and Advances</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>PBT</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>PR04020000</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Mortgages (Real Estate Secured)</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Loans</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>Total Product</t>
@@ -6700,133 +6700,133 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>769.6</v>
+        <v>1138.1</v>
       </c>
       <c r="O36" t="n">
-        <v>783.9</v>
+        <v>1108.7</v>
       </c>
       <c r="P36" t="n">
-        <v>767.9</v>
+        <v>1168.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>784.4</v>
+        <v>1131.6</v>
       </c>
       <c r="R36" t="n">
-        <v>787.6</v>
+        <v>1166.9</v>
       </c>
       <c r="S36" t="n">
-        <v>765.5</v>
+        <v>1147.5</v>
       </c>
       <c r="T36" t="n">
-        <v>793.6</v>
+        <v>1161.4</v>
       </c>
       <c r="U36" t="n">
-        <v>767.4</v>
+        <v>1116</v>
       </c>
       <c r="V36" t="n">
-        <v>798.2</v>
+        <v>1158.8</v>
       </c>
       <c r="W36" t="n">
-        <v>800.3</v>
+        <v>1120.3</v>
       </c>
       <c r="X36" t="n">
-        <v>787.7</v>
+        <v>1132.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>766.1</v>
+        <v>1162.9</v>
       </c>
       <c r="Z36" t="n">
-        <v>767.9</v>
+        <v>1168.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>765.5</v>
+        <v>1147.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>798.2</v>
+        <v>1158.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>766.1</v>
+        <v>1162.9</v>
       </c>
       <c r="AD36" t="n">
-        <v>743.7</v>
+        <v>1329.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>738.1</v>
+        <v>1278.9</v>
       </c>
       <c r="AF36" t="n">
-        <v>763.7</v>
+        <v>1281.7</v>
       </c>
       <c r="AG36" t="n">
-        <v>727.3</v>
+        <v>1295.9</v>
       </c>
       <c r="AH36" t="n">
-        <v>759.5</v>
+        <v>1305.1</v>
       </c>
       <c r="AI36" t="n">
-        <v>765.7</v>
+        <v>1294.6</v>
       </c>
       <c r="AJ36" t="n">
-        <v>762.1</v>
+        <v>1323.9</v>
       </c>
       <c r="AK36" t="n">
-        <v>728.6</v>
+        <v>1267.6</v>
       </c>
       <c r="AL36" t="n">
-        <v>756.4</v>
+        <v>1330.2</v>
       </c>
       <c r="AM36" t="n">
-        <v>762.8</v>
+        <v>1273.8</v>
       </c>
       <c r="AN36" t="n">
-        <v>724.2</v>
+        <v>1311.5</v>
       </c>
       <c r="AO36" t="n">
-        <v>736.9</v>
+        <v>1307.7</v>
       </c>
       <c r="AP36" t="n">
-        <v>763.7</v>
+        <v>1281.7</v>
       </c>
       <c r="AQ36" t="n">
-        <v>765.7</v>
+        <v>1294.6</v>
       </c>
       <c r="AR36" t="n">
-        <v>765.5</v>
+        <v>1147.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>765.7</v>
+        <v>1294.6</v>
       </c>
       <c r="AT36" t="n">
-        <v>765.9</v>
+        <v>1287.7</v>
       </c>
       <c r="AU36" t="n">
-        <v>766.1</v>
+        <v>1162.9</v>
       </c>
       <c r="AV36" t="n">
-        <v>736.9</v>
+        <v>1307.7</v>
       </c>
       <c r="AW36" t="n">
-        <v>767.8</v>
+        <v>1299.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MP90201010000</t>
+          <t>MP90101010000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Loans balance</t>
+          <t>Deposits balance</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Loans</t>
+          <t>Deposits</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Loan and Advances</t>
+          <t>Customer Deposits</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6875,287 +6875,987 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>660.2</v>
+        <v>642.2</v>
       </c>
       <c r="O37" t="n">
+        <v>632.4</v>
+      </c>
+      <c r="P37" t="n">
         <v>652.8</v>
       </c>
-      <c r="P37" t="n">
-        <v>641.7</v>
-      </c>
       <c r="Q37" t="n">
-        <v>647.4</v>
+        <v>653.4</v>
       </c>
       <c r="R37" t="n">
-        <v>646.6</v>
+        <v>641</v>
       </c>
       <c r="S37" t="n">
-        <v>677.3</v>
+        <v>630.3</v>
       </c>
       <c r="T37" t="n">
-        <v>667.1</v>
+        <v>641.6</v>
       </c>
       <c r="U37" t="n">
-        <v>675.7</v>
+        <v>627.5</v>
       </c>
       <c r="V37" t="n">
-        <v>646.9</v>
+        <v>628.3</v>
       </c>
       <c r="W37" t="n">
-        <v>671.3</v>
+        <v>639.9</v>
       </c>
       <c r="X37" t="n">
-        <v>644.8</v>
+        <v>626.9</v>
       </c>
       <c r="Y37" t="n">
-        <v>661.2</v>
+        <v>640.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>641.7</v>
+        <v>652.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>677.3</v>
+        <v>630.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>646.9</v>
+        <v>628.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>661.2</v>
+        <v>640.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>652.4</v>
+        <v>683.1</v>
       </c>
       <c r="AE37" t="n">
-        <v>641.7</v>
+        <v>663.9</v>
       </c>
       <c r="AF37" t="n">
-        <v>661.6</v>
+        <v>688.3</v>
       </c>
       <c r="AG37" t="n">
-        <v>649.2</v>
+        <v>665.6</v>
       </c>
       <c r="AH37" t="n">
-        <v>650.2</v>
+        <v>692.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>662</v>
+        <v>694.1</v>
       </c>
       <c r="AJ37" t="n">
-        <v>666.1</v>
+        <v>697.3</v>
       </c>
       <c r="AK37" t="n">
-        <v>650.1</v>
+        <v>703</v>
       </c>
       <c r="AL37" t="n">
-        <v>641.7</v>
+        <v>692.2</v>
       </c>
       <c r="AM37" t="n">
-        <v>657.4</v>
+        <v>695.6</v>
       </c>
       <c r="AN37" t="n">
-        <v>644.9</v>
+        <v>670.1</v>
       </c>
       <c r="AO37" t="n">
-        <v>634.5</v>
+        <v>702.4</v>
       </c>
       <c r="AP37" t="n">
-        <v>661.6</v>
+        <v>688.3</v>
       </c>
       <c r="AQ37" t="n">
-        <v>662</v>
+        <v>694.1</v>
       </c>
       <c r="AR37" t="n">
-        <v>677.3</v>
+        <v>630.3</v>
       </c>
       <c r="AS37" t="n">
-        <v>662</v>
+        <v>694.1</v>
       </c>
       <c r="AT37" t="n">
-        <v>667.7</v>
+        <v>663.9</v>
       </c>
       <c r="AU37" t="n">
-        <v>661.2</v>
+        <v>640.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>634.5</v>
+        <v>702.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>644.9</v>
+        <v>691.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>MP90101010000</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deposits balance</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Customer Deposits</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PR12200000</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Insurance Distribution</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1063</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1024.3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1058</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1016.1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1038.5</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1064.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1020.2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1023.6</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1038.7</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1027.1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1009.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1018.5</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1058</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1064.5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1038.7</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1018.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>973</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1019.2</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1003.9</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1016.7</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>973.4</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1010.2</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>998</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1016</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>969.6</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1022.6</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000.9</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>986.9</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1003.9</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1010.2</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1064.5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1010.2</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1004.4</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1018.5</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>986.9</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>MP90201010000</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Loans balance</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Loans</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Loan and Advances</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>PBT</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PR04004001</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Wealth Lending</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>934.5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>903.4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>924.6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>943.6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>921.6</v>
+      </c>
+      <c r="S39" t="n">
+        <v>925.9</v>
+      </c>
+      <c r="T39" t="n">
+        <v>906.6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>889.5</v>
+      </c>
+      <c r="V39" t="n">
+        <v>891.3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>897.6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>923.3</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>913.2</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>924.6</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>925.9</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>891.3</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>913.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>854.4</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>874</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>834.9</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>839.8</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>861.6</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>829.3</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>858.3</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>838.6</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>860.1</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>852.5</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>835</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>876.1</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>834.9</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>829.3</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>925.9</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>829.3</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>821.2</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>913.2</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>876.1</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>855.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MP90201010000</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Loans balance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Loan and Advances</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PR04020000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Mortgages (Real Estate Secured)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>567.6</v>
+      </c>
+      <c r="O40" t="n">
+        <v>560.4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>570.5</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>563.6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>580.4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>573.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>557</v>
+      </c>
+      <c r="U40" t="n">
+        <v>579.2</v>
+      </c>
+      <c r="V40" t="n">
+        <v>550</v>
+      </c>
+      <c r="W40" t="n">
+        <v>566.6</v>
+      </c>
+      <c r="X40" t="n">
+        <v>562.3</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>556.6</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>570.5</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>573.4</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>550</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>556.6</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>588.2</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>614.3</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>586.5</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>606</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>620.1</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>591.2</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>597.3</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>596.9</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>587.8</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>618.3</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>614.4</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>612</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>586.5</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>591.2</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>573.4</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>591.2</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>575</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>556.6</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>612</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>587.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MP90201010000</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Loans balance</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Loan and Advances</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PR05001000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Current Accounts Total</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Total Product</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>CG1010000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Retail Banking &amp; Wealth Management</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>IWPB</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>4040_1MGT</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>664.9</v>
+      </c>
+      <c r="O41" t="n">
+        <v>681.6</v>
+      </c>
+      <c r="P41" t="n">
+        <v>679.4</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>685.4</v>
+      </c>
+      <c r="R41" t="n">
+        <v>680</v>
+      </c>
+      <c r="S41" t="n">
+        <v>662.1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>673.7</v>
+      </c>
+      <c r="U41" t="n">
+        <v>668.9</v>
+      </c>
+      <c r="V41" t="n">
+        <v>683.1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>672.4</v>
+      </c>
+      <c r="X41" t="n">
+        <v>662</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>677.2</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>679.4</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>662.1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>683.1</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>677.2</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>641.2</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>613.2</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>638</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>605.6</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>614.8</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>613.9</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>614</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>639</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>628.7</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>631</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>630</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>641.7</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>638</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>613.9</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>662.1</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>613.9</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>618.2</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>677.2</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>641.7</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>629.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MP90201010000</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Loans balance</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Loan and Advances</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>PR12200000</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Insurance Distribution</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Total Product</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>CG1010000</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Retail Banking &amp; Wealth Management</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>IWPB</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>4040_1MGT</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v>690.2</v>
-      </c>
-      <c r="O38" t="n">
-        <v>695.1</v>
-      </c>
-      <c r="P38" t="n">
-        <v>715</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>707.2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>710.6</v>
-      </c>
-      <c r="S38" t="n">
-        <v>726.9</v>
-      </c>
-      <c r="T38" t="n">
-        <v>694.4</v>
-      </c>
-      <c r="U38" t="n">
-        <v>698.5</v>
-      </c>
-      <c r="V38" t="n">
-        <v>716.6</v>
-      </c>
-      <c r="W38" t="n">
-        <v>689.7</v>
-      </c>
-      <c r="X38" t="n">
-        <v>688.9</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>703.9</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>715</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>726.9</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>716.6</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>703.9</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>638.1</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>648</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>642.7</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>656.8</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>657.1</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>642</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>637.7</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>659</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>668.1</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>664.6</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>649.7</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>644.3</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>642.7</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>642</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>726.9</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>642</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>670.1</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>703.9</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>644.3</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>659.3</v>
+      <c r="N42" t="n">
+        <v>645</v>
+      </c>
+      <c r="O42" t="n">
+        <v>678.1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>647.6</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>643</v>
+      </c>
+      <c r="R42" t="n">
+        <v>646.1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>678.8</v>
+      </c>
+      <c r="T42" t="n">
+        <v>655.6</v>
+      </c>
+      <c r="U42" t="n">
+        <v>647.5</v>
+      </c>
+      <c r="V42" t="n">
+        <v>643</v>
+      </c>
+      <c r="W42" t="n">
+        <v>643.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>669.4</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>667.1</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>647.6</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>678.8</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>643</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>667.1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>711.9</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>713.6</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>685.2</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>707.4</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>697.8</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>717</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>687</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>691.1</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>687.2</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>683.9</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>718.2</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>716.7</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>685.2</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>717</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>678.8</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>717</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>735.5</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>667.1</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>716.7</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>695.6</v>
       </c>
     </row>
   </sheetData>
